--- a/raw/processedSamples/20260519_r2_CMH_USDA-blood_RT-QuIC.xlsx
+++ b/raw/processedSamples/20260519_r2_CMH_USDA-blood_RT-QuIC.xlsx
@@ -5,17 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MNPRO\Desktop\RT-QuIC Data\Caylie RT-QuIC and Nano-QuIc data\20260519_r2_CMH_USDA-blood_RT-QuIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Documents\Projects\usda-validation\raw\processedSamples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A218A0BE-AA72-456A-B800-292CA736CC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265A3AD5-EFA0-4242-9CD4-168AFC1EB985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4260" yWindow="1140" windowWidth="21600" windowHeight="13980" activeTab="2" xr2:uid="{CD32E0E8-2A1F-46CD-B5E6-D035360384A1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CD32E0E8-2A1F-46CD-B5E6-D035360384A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Cycle 1 (0 h)" sheetId="2" r:id="rId1"/>
     <sheet name="Table All Cycles" sheetId="1" r:id="rId2"/>
-    <sheet name="Curves" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -853,55 +852,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>74286</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>66048</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F69B9EB-DD3B-8F0C-C91B-31E1FB956FC4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="15314286" cy="5019048"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1324,37 +1274,37 @@
         <v>1000</v>
       </c>
       <c r="C16" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D16" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="E16" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F16" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="G16" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="H16" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I16" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="J16" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="K16" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="L16" s="12">
-        <v>100</v>
-      </c>
-      <c r="M16" s="13">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="M16" s="12">
+        <v>4</v>
       </c>
       <c r="O16" s="21"/>
     </row>
@@ -1365,38 +1315,38 @@
       <c r="B17" s="5">
         <v>1000</v>
       </c>
-      <c r="C17" s="14">
-        <v>100</v>
-      </c>
-      <c r="D17" s="14">
-        <v>100</v>
-      </c>
-      <c r="E17" s="14">
-        <v>100</v>
-      </c>
-      <c r="F17" s="14">
-        <v>100</v>
-      </c>
-      <c r="G17" s="14">
-        <v>100</v>
-      </c>
-      <c r="H17" s="14">
-        <v>100</v>
-      </c>
-      <c r="I17" s="14">
-        <v>100</v>
-      </c>
-      <c r="J17" s="14">
-        <v>100</v>
-      </c>
-      <c r="K17" s="14">
-        <v>100</v>
-      </c>
-      <c r="L17" s="14">
-        <v>100</v>
-      </c>
-      <c r="M17" s="15">
-        <v>100</v>
+      <c r="C17" s="12">
+        <v>4</v>
+      </c>
+      <c r="D17" s="12">
+        <v>4</v>
+      </c>
+      <c r="E17" s="12">
+        <v>4</v>
+      </c>
+      <c r="F17" s="12">
+        <v>4</v>
+      </c>
+      <c r="G17" s="12">
+        <v>4</v>
+      </c>
+      <c r="H17" s="12">
+        <v>4</v>
+      </c>
+      <c r="I17" s="12">
+        <v>4</v>
+      </c>
+      <c r="J17" s="12">
+        <v>4</v>
+      </c>
+      <c r="K17" s="12">
+        <v>4</v>
+      </c>
+      <c r="L17" s="12">
+        <v>4</v>
+      </c>
+      <c r="M17" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -1406,38 +1356,38 @@
       <c r="B18" s="5">
         <v>1000</v>
       </c>
-      <c r="C18" s="14">
-        <v>100</v>
-      </c>
-      <c r="D18" s="14">
-        <v>100</v>
-      </c>
-      <c r="E18" s="14">
-        <v>100</v>
-      </c>
-      <c r="F18" s="14">
-        <v>100</v>
-      </c>
-      <c r="G18" s="14">
-        <v>100</v>
-      </c>
-      <c r="H18" s="14">
-        <v>100</v>
-      </c>
-      <c r="I18" s="14">
-        <v>100</v>
-      </c>
-      <c r="J18" s="14">
-        <v>100</v>
-      </c>
-      <c r="K18" s="14">
-        <v>100</v>
-      </c>
-      <c r="L18" s="14">
-        <v>100</v>
-      </c>
-      <c r="M18" s="15">
-        <v>100</v>
+      <c r="C18" s="12">
+        <v>4</v>
+      </c>
+      <c r="D18" s="12">
+        <v>4</v>
+      </c>
+      <c r="E18" s="12">
+        <v>4</v>
+      </c>
+      <c r="F18" s="12">
+        <v>4</v>
+      </c>
+      <c r="G18" s="12">
+        <v>4</v>
+      </c>
+      <c r="H18" s="12">
+        <v>4</v>
+      </c>
+      <c r="I18" s="12">
+        <v>4</v>
+      </c>
+      <c r="J18" s="12">
+        <v>4</v>
+      </c>
+      <c r="K18" s="12">
+        <v>4</v>
+      </c>
+      <c r="L18" s="12">
+        <v>4</v>
+      </c>
+      <c r="M18" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -1447,38 +1397,38 @@
       <c r="B19" s="5">
         <v>1000</v>
       </c>
-      <c r="C19" s="14">
-        <v>100</v>
-      </c>
-      <c r="D19" s="14">
-        <v>100</v>
-      </c>
-      <c r="E19" s="14">
-        <v>100</v>
-      </c>
-      <c r="F19" s="14">
-        <v>100</v>
-      </c>
-      <c r="G19" s="14">
-        <v>100</v>
-      </c>
-      <c r="H19" s="14">
-        <v>100</v>
-      </c>
-      <c r="I19" s="14">
-        <v>100</v>
-      </c>
-      <c r="J19" s="14">
-        <v>100</v>
-      </c>
-      <c r="K19" s="14">
-        <v>100</v>
-      </c>
-      <c r="L19" s="14">
-        <v>100</v>
-      </c>
-      <c r="M19" s="15">
-        <v>100</v>
+      <c r="C19" s="12">
+        <v>4</v>
+      </c>
+      <c r="D19" s="12">
+        <v>4</v>
+      </c>
+      <c r="E19" s="12">
+        <v>4</v>
+      </c>
+      <c r="F19" s="12">
+        <v>4</v>
+      </c>
+      <c r="G19" s="12">
+        <v>4</v>
+      </c>
+      <c r="H19" s="12">
+        <v>4</v>
+      </c>
+      <c r="I19" s="12">
+        <v>4</v>
+      </c>
+      <c r="J19" s="12">
+        <v>4</v>
+      </c>
+      <c r="K19" s="12">
+        <v>4</v>
+      </c>
+      <c r="L19" s="12">
+        <v>4</v>
+      </c>
+      <c r="M19" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -1488,38 +1438,38 @@
       <c r="B20" s="5">
         <v>1000</v>
       </c>
-      <c r="C20" s="14">
-        <v>100</v>
-      </c>
-      <c r="D20" s="14">
-        <v>100</v>
-      </c>
-      <c r="E20" s="14">
-        <v>100</v>
-      </c>
-      <c r="F20" s="14">
-        <v>100</v>
-      </c>
-      <c r="G20" s="14">
-        <v>100</v>
-      </c>
-      <c r="H20" s="14">
-        <v>100</v>
-      </c>
-      <c r="I20" s="14">
-        <v>100</v>
-      </c>
-      <c r="J20" s="14">
-        <v>100</v>
-      </c>
-      <c r="K20" s="14">
-        <v>100</v>
-      </c>
-      <c r="L20" s="14">
-        <v>100</v>
-      </c>
-      <c r="M20" s="15">
-        <v>100</v>
+      <c r="C20" s="12">
+        <v>4</v>
+      </c>
+      <c r="D20" s="12">
+        <v>4</v>
+      </c>
+      <c r="E20" s="12">
+        <v>4</v>
+      </c>
+      <c r="F20" s="12">
+        <v>4</v>
+      </c>
+      <c r="G20" s="12">
+        <v>4</v>
+      </c>
+      <c r="H20" s="12">
+        <v>4</v>
+      </c>
+      <c r="I20" s="12">
+        <v>4</v>
+      </c>
+      <c r="J20" s="12">
+        <v>4</v>
+      </c>
+      <c r="K20" s="12">
+        <v>4</v>
+      </c>
+      <c r="L20" s="12">
+        <v>4</v>
+      </c>
+      <c r="M20" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1529,38 +1479,38 @@
       <c r="B21" s="5">
         <v>1000</v>
       </c>
-      <c r="C21" s="14">
-        <v>100</v>
-      </c>
-      <c r="D21" s="14">
-        <v>100</v>
-      </c>
-      <c r="E21" s="14">
-        <v>100</v>
-      </c>
-      <c r="F21" s="14">
-        <v>100</v>
-      </c>
-      <c r="G21" s="14">
-        <v>100</v>
-      </c>
-      <c r="H21" s="14">
-        <v>100</v>
-      </c>
-      <c r="I21" s="14">
-        <v>100</v>
-      </c>
-      <c r="J21" s="14">
-        <v>100</v>
-      </c>
-      <c r="K21" s="14">
-        <v>100</v>
-      </c>
-      <c r="L21" s="14">
-        <v>100</v>
-      </c>
-      <c r="M21" s="15">
-        <v>100</v>
+      <c r="C21" s="12">
+        <v>4</v>
+      </c>
+      <c r="D21" s="12">
+        <v>4</v>
+      </c>
+      <c r="E21" s="12">
+        <v>4</v>
+      </c>
+      <c r="F21" s="12">
+        <v>4</v>
+      </c>
+      <c r="G21" s="12">
+        <v>4</v>
+      </c>
+      <c r="H21" s="12">
+        <v>4</v>
+      </c>
+      <c r="I21" s="12">
+        <v>4</v>
+      </c>
+      <c r="J21" s="12">
+        <v>4</v>
+      </c>
+      <c r="K21" s="12">
+        <v>4</v>
+      </c>
+      <c r="L21" s="12">
+        <v>4</v>
+      </c>
+      <c r="M21" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -1570,38 +1520,38 @@
       <c r="B22" s="5">
         <v>1000</v>
       </c>
-      <c r="C22" s="14">
-        <v>100</v>
-      </c>
-      <c r="D22" s="14">
-        <v>100</v>
-      </c>
-      <c r="E22" s="14">
-        <v>100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>100</v>
-      </c>
-      <c r="G22" s="14">
-        <v>100</v>
-      </c>
-      <c r="H22" s="14">
-        <v>100</v>
-      </c>
-      <c r="I22" s="14">
-        <v>100</v>
-      </c>
-      <c r="J22" s="14">
-        <v>100</v>
-      </c>
-      <c r="K22" s="14">
-        <v>100</v>
-      </c>
-      <c r="L22" s="14">
-        <v>100</v>
-      </c>
-      <c r="M22" s="15">
-        <v>100</v>
+      <c r="C22" s="12">
+        <v>4</v>
+      </c>
+      <c r="D22" s="12">
+        <v>4</v>
+      </c>
+      <c r="E22" s="12">
+        <v>4</v>
+      </c>
+      <c r="F22" s="12">
+        <v>4</v>
+      </c>
+      <c r="G22" s="12">
+        <v>4</v>
+      </c>
+      <c r="H22" s="12">
+        <v>4</v>
+      </c>
+      <c r="I22" s="12">
+        <v>4</v>
+      </c>
+      <c r="J22" s="12">
+        <v>4</v>
+      </c>
+      <c r="K22" s="12">
+        <v>4</v>
+      </c>
+      <c r="L22" s="12">
+        <v>4</v>
+      </c>
+      <c r="M22" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -1611,38 +1561,38 @@
       <c r="B23" s="16">
         <v>1000</v>
       </c>
-      <c r="C23" s="17">
-        <v>100</v>
-      </c>
-      <c r="D23" s="17">
-        <v>100</v>
-      </c>
-      <c r="E23" s="17">
-        <v>100</v>
-      </c>
-      <c r="F23" s="17">
-        <v>100</v>
-      </c>
-      <c r="G23" s="17">
-        <v>100</v>
-      </c>
-      <c r="H23" s="17">
-        <v>100</v>
-      </c>
-      <c r="I23" s="17">
-        <v>100</v>
-      </c>
-      <c r="J23" s="17">
-        <v>100</v>
-      </c>
-      <c r="K23" s="17">
-        <v>100</v>
-      </c>
-      <c r="L23" s="17">
-        <v>100</v>
-      </c>
-      <c r="M23" s="18">
-        <v>100</v>
+      <c r="C23" s="12">
+        <v>4</v>
+      </c>
+      <c r="D23" s="12">
+        <v>4</v>
+      </c>
+      <c r="E23" s="12">
+        <v>4</v>
+      </c>
+      <c r="F23" s="12">
+        <v>4</v>
+      </c>
+      <c r="G23" s="12">
+        <v>4</v>
+      </c>
+      <c r="H23" s="12">
+        <v>4</v>
+      </c>
+      <c r="I23" s="12">
+        <v>4</v>
+      </c>
+      <c r="J23" s="12">
+        <v>4</v>
+      </c>
+      <c r="K23" s="12">
+        <v>4</v>
+      </c>
+      <c r="L23" s="12">
+        <v>4</v>
+      </c>
+      <c r="M23" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -89168,18 +89118,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBFF9095-D4B9-45B0-BEC5-7A6A387455BC}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="38" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>